--- a/producao/pressupostos/PRESSUPOSTO_REAL_YAMAHA_ITURAN.xlsx
+++ b/producao/pressupostos/PRESSUPOSTO_REAL_YAMAHA_ITURAN.xlsx
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="F12" s="9" t="n">
-        <v>46245</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="13">
@@ -791,7 +791,7 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="D13" s="8" t="n"/>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="F22" s="18" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="23">
@@ -1661,21 +1661,17 @@
         <v>3</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="G6" s="36">
         <f>IF(OR(E6="",F6=""),"",ROUND(E6*F6,2))</f>
         <v/>
       </c>
-      <c r="H6" s="15" t="inlineStr">
-        <is>
-          <t>A PAGAR</t>
-        </is>
-      </c>
+      <c r="H6" s="15" t="inlineStr"/>
       <c r="I6" s="14" t="n"/>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>padrão real — 1.500/diária quando opera (YAH CHURCH). Zerar se aqui for só interface.</t>
+          <t>SALÁRIO FIXO — equipe da casa, não é custo deste job (a preço de mercado seriam 1.500/diária)</t>
         </is>
       </c>
     </row>
@@ -1687,33 +1683,29 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Direção de fotografia</t>
+          <t>Acsa</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>a definir</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="E7" s="15" t="n">
         <v>3</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="G7" s="36">
         <f>IF(OR(E7="",F7=""),"",ROUND(E7*F7,2))</f>
         <v/>
       </c>
-      <c r="H7" s="15" t="inlineStr">
-        <is>
-          <t>A PAGAR</t>
-        </is>
-      </c>
+      <c r="H7" s="15" t="inlineStr"/>
       <c r="I7" s="14" t="n"/>
       <c r="J7" s="12" t="inlineStr">
         <is>
-          <t>ESTIMADO — mesmo valor usado no Manente</t>
+          <t>SALÁRIO FIXO — equipe da casa, não é custo deste job (referência 700/diária)</t>
         </is>
       </c>
     </row>
@@ -1725,33 +1717,29 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Produção</t>
+          <t>Thiago</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>a definir</t>
+          <t>DOP / Operador de câmera 1</t>
         </is>
       </c>
       <c r="E8" s="15" t="n">
         <v>3</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="G8" s="36">
         <f>IF(OR(E8="",F8=""),"",ROUND(E8*F8,2))</f>
         <v/>
       </c>
-      <c r="H8" s="15" t="inlineStr">
-        <is>
-          <t>A PAGAR</t>
-        </is>
-      </c>
+      <c r="H8" s="15" t="inlineStr"/>
       <c r="I8" s="14" t="n"/>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>ESTIMADO — padrão de produtor técnico</t>
+          <t>SALÁRIO FIXO — acumula fotografia e câmera 1 (referência 1.200 + 1.000/diária)</t>
         </is>
       </c>
     </row>
@@ -1763,33 +1751,29 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Operador de câmera 1</t>
+          <t>Rodrigo</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Canon C400</t>
+          <t>Operador de câmera 2</t>
         </is>
       </c>
       <c r="E9" s="15" t="n">
         <v>3</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="G9" s="36">
         <f>IF(OR(E9="",F9=""),"",ROUND(E9*F9,2))</f>
         <v/>
       </c>
-      <c r="H9" s="15" t="inlineStr">
-        <is>
-          <t>A PAGAR</t>
-        </is>
-      </c>
+      <c r="H9" s="15" t="inlineStr"/>
       <c r="I9" s="14" t="n"/>
       <c r="J9" s="12" t="inlineStr">
         <is>
-          <t>padrão real da casa — YAH CHURCH</t>
+          <t>SALÁRIO FIXO — equipe da casa, não é custo deste job (referência 1.000/diária)</t>
         </is>
       </c>
     </row>
@@ -1801,33 +1785,29 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Operador de câmera 2</t>
+          <t>Viny</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Canon C400</t>
+          <t>Resolume / teleprompter</t>
         </is>
       </c>
       <c r="E10" s="15" t="n">
         <v>3</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="G10" s="36">
         <f>IF(OR(E10="",F10=""),"",ROUND(E10*F10,2))</f>
         <v/>
       </c>
-      <c r="H10" s="15" t="inlineStr">
-        <is>
-          <t>A PAGAR</t>
-        </is>
-      </c>
+      <c r="H10" s="15" t="inlineStr"/>
       <c r="I10" s="14" t="n"/>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>padrão real da casa — YAH CHURCH</t>
+          <t>SALÁRIO FIXO — equipe da casa, não é custo deste job (referência 700/diária)</t>
         </is>
       </c>
     </row>
@@ -1839,33 +1819,29 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Assistente 1</t>
+          <t>Edhen</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>assistência de set</t>
+          <t>Som direto</t>
         </is>
       </c>
       <c r="E11" s="15" t="n">
         <v>3</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="G11" s="36">
         <f>IF(OR(E11="",F11=""),"",ROUND(E11*F11,2))</f>
         <v/>
       </c>
-      <c r="H11" s="15" t="inlineStr">
-        <is>
-          <t>A PAGAR</t>
-        </is>
-      </c>
+      <c r="H11" s="15" t="inlineStr"/>
       <c r="I11" s="14" t="n"/>
       <c r="J11" s="12" t="inlineStr">
         <is>
-          <t>padrão real da casa — YAH CHURCH</t>
+          <t>SALÁRIO FIXO — equipe da casa, não é custo deste job (referência 700/diária)</t>
         </is>
       </c>
     </row>
@@ -1877,33 +1853,29 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Assistente 2</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>assistência de set</t>
+          <t>Continuidade / script</t>
         </is>
       </c>
       <c r="E12" s="15" t="n">
         <v>3</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="G12" s="36">
         <f>IF(OR(E12="",F12=""),"",ROUND(E12*F12,2))</f>
         <v/>
       </c>
-      <c r="H12" s="15" t="inlineStr">
-        <is>
-          <t>A PAGAR</t>
-        </is>
-      </c>
+      <c r="H12" s="15" t="inlineStr"/>
       <c r="I12" s="14" t="n"/>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>padrão real da casa — YAH CHURCH</t>
+          <t>SALÁRIO FIXO — equipe da casa, não é custo deste job (referência 500/diária)</t>
         </is>
       </c>
     </row>
@@ -1915,58 +1887,52 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Áudio</t>
+          <t>Operação de luz / grip</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>som direto</t>
+          <t>Aputure 1200x, Infinibar, caixa 4×4 m</t>
         </is>
       </c>
       <c r="E13" s="15" t="n">
         <v>3</v>
       </c>
       <c r="F13" s="13" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="G13" s="36">
         <f>IF(OR(E13="",F13=""),"",ROUND(E13*F13,2))</f>
         <v/>
       </c>
-      <c r="H13" s="15" t="inlineStr">
-        <is>
-          <t>A PAGAR</t>
-        </is>
-      </c>
+      <c r="H13" s="15" t="inlineStr"/>
       <c r="I13" s="14" t="n"/>
       <c r="J13" s="12" t="inlineStr">
         <is>
-          <t>ESTIMADO — consta no bloco 'Direção e equipe de set'</t>
+          <t>SALÁRIO FIXO — absorvido pela própria equipe da casa; se entrar gripeiro de fora, lançar aqui</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>EQUIPE DE SET</t>
+          <t>DADOS E MÍDIA</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Making of</t>
+          <t>HD 24TB</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>registro</t>
+          <t>Mídia, armazenamento e uploads</t>
         </is>
       </c>
       <c r="E14" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" s="13" t="n">
-        <v>500</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F14" s="16" t="n"/>
       <c r="G14" s="36">
         <f>IF(OR(E14="",F14=""),"",ROUND(E14*F14,2))</f>
         <v/>
@@ -1979,195 +1945,177 @@
       <c r="I14" s="14" t="n"/>
       <c r="J14" s="12" t="inlineStr">
         <is>
-          <t>ESTIMADO — consta no escopo vendido</t>
+          <t>EM BRANCO — referência da novela vertical: HD de 24 TB a R$ 3.500</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>EQUIPE DE SET</t>
+          <t>PÓS-PRODUÇÃO</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Continuidade</t>
+          <t>Montagem dos 10 filmes</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>script</t>
+          <t>até 8 min cada</t>
         </is>
       </c>
       <c r="E15" s="15" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F15" s="13" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G15" s="36">
         <f>IF(OR(E15="",F15=""),"",ROUND(E15*F15,2))</f>
         <v/>
       </c>
-      <c r="H15" s="15" t="inlineStr">
-        <is>
-          <t>A PAGAR</t>
-        </is>
-      </c>
+      <c r="H15" s="15" t="inlineStr"/>
       <c r="I15" s="14" t="n"/>
       <c r="J15" s="12" t="inlineStr">
         <is>
-          <t>ESTIMADO — consta no escopo vendido; com 10 procedimentos técnicos é função crítica</t>
+          <t>pós interna — sem custo de terceiro. Se alguém receber cachê por este job, lançar aqui.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>EQUIPE DE SET</t>
+          <t>PÓS-PRODUÇÃO</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Operação de luz / grip</t>
+          <t>Abertura, encerramento e grafismos</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Aputure 1200x, Infinibar, caixa 4×4 m</t>
+          <t>padronizados</t>
         </is>
       </c>
       <c r="E16" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="G16" s="36">
         <f>IF(OR(E16="",F16=""),"",ROUND(E16*F16,2))</f>
         <v/>
       </c>
-      <c r="H16" s="15" t="inlineStr">
-        <is>
-          <t>A PAGAR</t>
-        </is>
-      </c>
+      <c r="H16" s="15" t="inlineStr"/>
       <c r="I16" s="14" t="n"/>
       <c r="J16" s="12" t="inlineStr">
         <is>
-          <t>ESTIMADO — o bloco 'Iluminação e grip' vende a operação junto</t>
+          <t>pós interna — sem custo de terceiro</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>EQUIPE DE SET</t>
+          <t>PÓS-PRODUÇÃO</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Operador de Resolume e playback</t>
+          <t>Tratamento de cor</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>cues, conversão e testes</t>
+          <t>10 filmes</t>
         </is>
       </c>
       <c r="E17" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F17" s="13" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="G17" s="36">
         <f>IF(OR(E17="",F17=""),"",ROUND(E17*F17,2))</f>
         <v/>
       </c>
-      <c r="H17" s="15" t="inlineStr">
-        <is>
-          <t>A PAGAR</t>
-        </is>
-      </c>
+      <c r="H17" s="15" t="inlineStr"/>
       <c r="I17" s="14" t="n"/>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>ESTIMADO — bloco próprio na proposta, com operador incluso · na BYD o Resolume saiu 1.000 por pacote</t>
+          <t>pós interna — sem custo de terceiro</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>DADOS E MÍDIA</t>
+          <t>PÓS-PRODUÇÃO</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>DIT</t>
+          <t>Mixagem de áudio</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>checksum, cópias e uploads</t>
+          <t>10 filmes</t>
         </is>
       </c>
       <c r="E18" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G18" s="36">
         <f>IF(OR(E18="",F18=""),"",ROUND(E18*F18,2))</f>
         <v/>
       </c>
-      <c r="H18" s="15" t="inlineStr">
-        <is>
-          <t>A PAGAR</t>
-        </is>
-      </c>
+      <c r="H18" s="15" t="inlineStr"/>
       <c r="I18" s="14" t="n"/>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>ESTIMADO — bloco 'Dados e logística' da proposta</t>
+          <t>pós interna — sem custo de terceiro</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>DADOS E MÍDIA</t>
+          <t>PÓS-PRODUÇÃO</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Mídia, armazenamento e uploads</t>
+          <t>Legendas em português</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>10 filmes 4K · masters e cópias operacionais</t>
+          <t>10 filmes</t>
         </is>
       </c>
       <c r="E19" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="16" t="n"/>
+      <c r="F19" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="G19" s="36">
         <f>IF(OR(E19="",F19=""),"",ROUND(E19*F19,2))</f>
         <v/>
       </c>
-      <c r="H19" s="15" t="inlineStr">
-        <is>
-          <t>A PAGAR</t>
-        </is>
-      </c>
+      <c r="H19" s="15" t="inlineStr"/>
       <c r="I19" s="14" t="n"/>
       <c r="J19" s="12" t="inlineStr">
         <is>
-          <t>ADICIONADO — vendido no escopo</t>
+          <t>pós interna — sem custo de terceiro</t>
         </is>
       </c>
     </row>
@@ -2179,80 +2127,86 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>Montagem dos 10 filmes</t>
+          <t>Roteiros e matriz técnica</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>até 8 min cada</t>
+          <t>10 roteiros + decupagem</t>
         </is>
       </c>
       <c r="E20" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="F20" s="13" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F20" s="16" t="n"/>
       <c r="G20" s="36">
         <f>IF(OR(E20="",F20=""),"",ROUND(E20*F20,2))</f>
         <v/>
       </c>
-      <c r="H20" s="15" t="inlineStr"/>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>A PAGAR</t>
+        </is>
+      </c>
       <c r="I20" s="14" t="n"/>
       <c r="J20" s="12" t="inlineStr">
         <is>
-          <t>padrão da casa — pós interna, sem custo de terceiro. Se alguém receber cachê por este job, lançar aqui.</t>
+          <t>EM BRANCO — etapa 01 do plano de produção; zerar se for interno, lançar se for roteirista contratado</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>PÓS-PRODUÇÃO</t>
+          <t>ESTÚDIO E LED</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Abertura, encerramento e grafismos</t>
+          <t>Estúdio YAD Morumbi</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>padronizados</t>
+          <t>3 diárias de até 10h</t>
         </is>
       </c>
       <c r="E21" s="15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="G21" s="36">
         <f>IF(OR(E21="",F21=""),"",ROUND(E21*F21,2))</f>
         <v/>
       </c>
-      <c r="H21" s="15" t="inlineStr"/>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>A PAGAR</t>
+        </is>
+      </c>
       <c r="I21" s="14" t="n"/>
       <c r="J21" s="12" t="inlineStr">
         <is>
-          <t>padrão da casa — pós interna, sem custo de terceiro</t>
+          <t>custo interno de ocupação, R$ 3.000/diária — mesmo critério do Manente · transferência entre unidades, volta para o grupo</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>PÓS-PRODUÇÃO</t>
+          <t>ESTÚDIO E LED</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>Tratamento de cor</t>
+          <t>Montagem e desmontagem do painel de LED</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>10 filmes</t>
+          <t>estrutura, alinhamento e teste de câmera</t>
         </is>
       </c>
       <c r="E22" s="15" t="n">
@@ -2269,28 +2223,28 @@
       <c r="I22" s="14" t="n"/>
       <c r="J22" s="12" t="inlineStr">
         <is>
-          <t>padrão da casa — pós interna, sem custo de terceiro</t>
+          <t>montagem feita pela própria equipe da casa — sem o custo de 2.700 que o Natan cobrou na live da BYD</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>PÓS-PRODUÇÃO</t>
+          <t>ESTÚDIO E LED</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Mixagem de áudio</t>
+          <t>Painel indoor, processadora e cabeamento</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>10 filmes</t>
+          <t>estrutura própria</t>
         </is>
       </c>
       <c r="E23" s="15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" s="13" t="n">
         <v>0</v>
@@ -2303,101 +2257,103 @@
       <c r="I23" s="14" t="n"/>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>padrão da casa — pós interna, sem custo de terceiro</t>
+          <t>parede de LED da unidade do Morumbi — sem locação</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>PÓS-PRODUÇÃO</t>
+          <t>EQUIPAMENTO E ENERGIA</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Legendas em português</t>
+          <t>Gerador e energia dedicada</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>10 filmes</t>
+          <t>gerador, geradorista, combustível, distribuição e aterramento</t>
         </is>
       </c>
       <c r="E24" s="15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G24" s="36">
         <f>IF(OR(E24="",F24=""),"",ROUND(E24*F24,2))</f>
         <v/>
       </c>
-      <c r="H24" s="15" t="inlineStr"/>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>A PAGAR</t>
+        </is>
+      </c>
       <c r="I24" s="14" t="n"/>
       <c r="J24" s="12" t="inlineStr">
         <is>
-          <t>padrão da casa — pós interna, sem custo de terceiro</t>
+          <t>R$ 1.000/diária em estúdio — no Manente, em locação, o mesmo item saiu 6.000 pelo projeto</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>PÓS-PRODUÇÃO</t>
+          <t>EQUIPAMENTO E ENERGIA</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Roteiros e matriz técnica</t>
+          <t>Canon C400, Cine-Servo PL, luz e grip</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>10 roteiros + decupagem</t>
+          <t>parque próprio</t>
         </is>
       </c>
       <c r="E25" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="16" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="G25" s="36">
         <f>IF(OR(E25="",F25=""),"",ROUND(E25*F25,2))</f>
         <v/>
       </c>
-      <c r="H25" s="15" t="inlineStr">
-        <is>
-          <t>A PAGAR</t>
-        </is>
-      </c>
+      <c r="H25" s="15" t="inlineStr"/>
       <c r="I25" s="14" t="n"/>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>ADICIONADO — etapa 01 do plano de produção; definir se é interno ou roteirista contratado</t>
+          <t>equipamento da casa — sem locação</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>ESTÚDIO E LED</t>
+          <t>ALIMENTAÇÃO</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>Estúdio YAD Morumbi</t>
+          <t>Alimentação da equipe</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>3 diárias de até 10h</t>
+          <t>7 pessoas × 3 diárias</t>
         </is>
       </c>
       <c r="E26" s="15" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>3000</v>
+        <v>200</v>
       </c>
       <c r="G26" s="36">
         <f>IF(OR(E26="",F26=""),"",ROUND(E26*F26,2))</f>
@@ -2411,31 +2367,31 @@
       <c r="I26" s="14" t="n"/>
       <c r="J26" s="12" t="inlineStr">
         <is>
-          <t>custo interno de ocupação, R$ 3.000/diária — mesmo critério do Manente · transferência entre unidades</t>
+          <t>R$ 200 por pessoa/diária — número real da casa em estúdio</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>ESTÚDIO E LED</t>
+          <t>PRODUÇÃO E DIVERSOS</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Montagem e desmontagem do painel de LED</t>
+          <t>Transporte local e estacionamento</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>estrutura, alinhamento e teste de câmera</t>
+          <t>3 diárias (ida e volta)</t>
         </is>
       </c>
       <c r="E27" s="15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F27" s="13" t="n">
-        <v>2700</v>
+        <v>350</v>
       </c>
       <c r="G27" s="36">
         <f>IF(OR(E27="",F27=""),"",ROUND(E27*F27,2))</f>
@@ -2449,64 +2405,71 @@
       <c r="I27" s="14" t="n"/>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>padrão real — Natan cobrou 2.700 pela montagem e desmontagem do painel na live da BYD</t>
+          <t>R$ 350 por trecho, 2 trechos por diária</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>ESTÚDIO E LED</t>
+          <t>PRODUÇÃO E DIVERSOS</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>Painel indoor, processadora e cabeamento</t>
+          <t>Consumíveis de set</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>estrutura própria</t>
+          <t>fitas, pilhas, materiais</t>
         </is>
       </c>
       <c r="E28" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G28" s="36">
         <f>IF(OR(E28="",F28=""),"",ROUND(E28*F28,2))</f>
         <v/>
       </c>
-      <c r="H28" s="15" t="inlineStr"/>
+      <c r="H28" s="15" t="inlineStr">
+        <is>
+          <t>A PAGAR</t>
+        </is>
+      </c>
       <c r="I28" s="14" t="n"/>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>parede de LED da unidade do Morumbi — sem locação</t>
+          <t>verba fechada</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>EQUIPAMENTO E ENERGIA</t>
+          <t>COMISSÃO</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Gerador e energia dedicada</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>gerador, geradorista, combustível, distribuição e aterramento</t>
-        </is>
-      </c>
-      <c r="E29" s="15" t="n">
+          <t>% sobre a entrada líquida</t>
+        </is>
+      </c>
+      <c r="E29" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="16" t="n"/>
+      <c r="F29" s="36">
+        <f>ROUND(RESUMO!$C$24*RESUMO!$F$22,2)</f>
+        <v/>
+      </c>
       <c r="G29" s="36">
         <f>IF(OR(E29="",F29=""),"",ROUND(E29*F29,2))</f>
         <v/>
@@ -2517,193 +2480,80 @@
         </is>
       </c>
       <c r="I29" s="14" t="n"/>
-      <c r="J29" s="12" t="inlineStr">
-        <is>
-          <t>vendido dentro do pacote · no Manente o gerador saiu R$ 6.000 pelo projeto</t>
-        </is>
+      <c r="J29" s="12">
+        <f>TEXT(RESUMO!$F$22,"0.0%")&amp;" da entrada líquida (RESUMO!C24)"</f>
+        <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>EQUIPAMENTO E ENERGIA</t>
-        </is>
-      </c>
-      <c r="C30" s="12" t="inlineStr">
-        <is>
-          <t>Canon C400, Cine-Servo PL, luz e grip</t>
-        </is>
-      </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>parque próprio</t>
-        </is>
-      </c>
-      <c r="E30" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F30" s="13" t="n">
-        <v>0</v>
-      </c>
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="38" t="n"/>
+      <c r="F30" s="16" t="n"/>
       <c r="G30" s="36">
         <f>IF(OR(E30="",F30=""),"",ROUND(E30*F30,2))</f>
         <v/>
       </c>
-      <c r="H30" s="15" t="inlineStr"/>
+      <c r="H30" s="15" t="n"/>
       <c r="I30" s="14" t="n"/>
-      <c r="J30" s="12" t="inlineStr">
-        <is>
-          <t>equipamento da casa — confirmar se a C400 e as Cine-Servo são próprias ou locadas</t>
-        </is>
-      </c>
+      <c r="J30" s="12" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>ALIMENTAÇÃO</t>
-        </is>
-      </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>Alimentação da equipe</t>
-        </is>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>13 pessoas × 3 diárias</t>
-        </is>
-      </c>
-      <c r="E31" s="15" t="n">
-        <v>39</v>
-      </c>
-      <c r="F31" s="13" t="n">
-        <v>100</v>
-      </c>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="38" t="n"/>
+      <c r="F31" s="16" t="n"/>
       <c r="G31" s="36">
         <f>IF(OR(E31="",F31=""),"",ROUND(E31*F31,2))</f>
         <v/>
       </c>
-      <c r="H31" s="15" t="inlineStr">
-        <is>
-          <t>A PAGAR</t>
-        </is>
-      </c>
+      <c r="H31" s="15" t="n"/>
       <c r="I31" s="14" t="n"/>
-      <c r="J31" s="12" t="inlineStr">
-        <is>
-          <t>ESTIMADO — a proposta vende alimentação dentro do bloco 'Dados e logística'</t>
-        </is>
-      </c>
+      <c r="J31" s="12" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="12" t="inlineStr">
-        <is>
-          <t>PRODUÇÃO E DIVERSOS</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>Transporte local e estacionamento</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>3 diárias</t>
-        </is>
-      </c>
-      <c r="E32" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="38" t="n"/>
       <c r="F32" s="16" t="n"/>
       <c r="G32" s="36">
         <f>IF(OR(E32="",F32=""),"",ROUND(E32*F32,2))</f>
         <v/>
       </c>
-      <c r="H32" s="15" t="inlineStr">
-        <is>
-          <t>A PAGAR</t>
-        </is>
-      </c>
+      <c r="H32" s="15" t="n"/>
       <c r="I32" s="14" t="n"/>
-      <c r="J32" s="12" t="inlineStr">
-        <is>
-          <t>ADICIONADO — vendido no escopo</t>
-        </is>
-      </c>
+      <c r="J32" s="12" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>PRODUÇÃO E DIVERSOS</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>Consumíveis de set</t>
-        </is>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>fitas, pilhas, materiais</t>
-        </is>
-      </c>
-      <c r="E33" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="38" t="n"/>
       <c r="F33" s="16" t="n"/>
       <c r="G33" s="36">
         <f>IF(OR(E33="",F33=""),"",ROUND(E33*F33,2))</f>
         <v/>
       </c>
-      <c r="H33" s="15" t="inlineStr">
-        <is>
-          <t>A PAGAR</t>
-        </is>
-      </c>
+      <c r="H33" s="15" t="n"/>
       <c r="I33" s="14" t="n"/>
-      <c r="J33" s="12" t="inlineStr">
-        <is>
-          <t>ADICIONADO</t>
-        </is>
-      </c>
+      <c r="J33" s="12" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>COMISSÃO</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>Comissão comercial</t>
-        </is>
-      </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>% sobre a entrada líquida</t>
-        </is>
-      </c>
-      <c r="E34" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="36">
-        <f>ROUND(RESUMO!$C$24*RESUMO!$F$22,2)</f>
-        <v/>
-      </c>
+      <c r="B34" s="12" t="n"/>
+      <c r="C34" s="12" t="n"/>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="38" t="n"/>
+      <c r="F34" s="16" t="n"/>
       <c r="G34" s="36">
         <f>IF(OR(E34="",F34=""),"",ROUND(E34*F34,2))</f>
         <v/>
       </c>
-      <c r="H34" s="15" t="inlineStr">
-        <is>
-          <t>A PAGAR</t>
-        </is>
-      </c>
+      <c r="H34" s="15" t="n"/>
       <c r="I34" s="14" t="n"/>
-      <c r="J34" s="12">
-        <f>TEXT(RESUMO!$F$22,"0.0%")&amp;" da entrada líquida (RESUMO!C24)"</f>
-        <v/>
-      </c>
+      <c r="J34" s="12" t="n"/>
     </row>
     <row r="35">
       <c r="B35" s="12" t="n"/>
